--- a/CRONUSA_data.xlsx
+++ b/CRONUSA_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdrebber/Desktop/Miines/Research/Chapter 1/CRONUS-A Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdrebber/Desktop/Miines/Research/Chapter 1/14C_Ant_Production_Rate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3EC56F-ECF8-804F-8339-B2EFE6801E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF58F324-E26B-DF46-BCBA-E8C2FE4E32CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-1960" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{96286E7B-7EC2-434B-98B3-5415A69C7BB4}"/>
+    <workbookView xWindow="9220" yWindow="760" windowWidth="21020" windowHeight="18880" activeTab="1" xr2:uid="{96286E7B-7EC2-434B-98B3-5415A69C7BB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Table" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="188">
   <si>
     <t>Date Extracted</t>
   </si>
@@ -643,13 +643,34 @@
   </si>
   <si>
     <t>Intercomparison</t>
+  </si>
+  <si>
+    <t>CRONUS-A-01</t>
+  </si>
+  <si>
+    <t>CRONUS-A-10 static</t>
+  </si>
+  <si>
+    <t>CRONUS-A-11 static</t>
+  </si>
+  <si>
+    <t>CRONUS-A-12</t>
+  </si>
+  <si>
+    <t>CRONUS-A-13 static</t>
+  </si>
+  <si>
+    <t>CRONUS-A-15 static</t>
+  </si>
+  <si>
+    <t>CRONUS-A-16 static</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -657,9 +678,10 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="170" formatCode="0.0000E+00"/>
-    <numFmt numFmtId="173" formatCode="m/d/yyyy;@"/>
+    <numFmt numFmtId="171" formatCode="m/d/yyyy;@"/>
+    <numFmt numFmtId="172" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -683,6 +705,16 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
@@ -746,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -833,10 +865,76 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7072,19 +7170,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539433E8-C32A-C34A-A35C-D716F459AA35}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="19.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="1"/>
+    <col min="1" max="1" width="26.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="103.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="19.33203125" style="1"/>
   </cols>
   <sheetData>
@@ -9172,7 +9269,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>142</v>
       </c>
@@ -9191,16 +9288,20 @@
       <c r="F73" s="2">
         <v>2.0148000000000001</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="26">
+      <c r="G73" s="43">
+        <v>1498500</v>
+      </c>
+      <c r="H73" s="43">
+        <v>12365</v>
+      </c>
+      <c r="I73" s="44">
         <v>727700</v>
       </c>
-      <c r="J73" s="26">
+      <c r="J73" s="44">
         <v>8000</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>143</v>
       </c>
@@ -9219,16 +9320,20 @@
       <c r="F74" s="2">
         <v>2.2967</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="26">
+      <c r="G74" s="43">
+        <v>1698800</v>
+      </c>
+      <c r="H74" s="43">
+        <v>14554</v>
+      </c>
+      <c r="I74" s="44">
         <v>725600</v>
       </c>
-      <c r="J74" s="26">
+      <c r="J74" s="44">
         <v>7700</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>144</v>
       </c>
@@ -9247,16 +9352,20 @@
       <c r="F75" s="2">
         <v>2.9811000000000001</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="26">
+      <c r="G75" s="43">
+        <v>2198500</v>
+      </c>
+      <c r="H75" s="43">
+        <v>18248</v>
+      </c>
+      <c r="I75" s="44">
         <v>726600</v>
       </c>
-      <c r="J75" s="26">
+      <c r="J75" s="44">
         <v>7000</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>145</v>
       </c>
@@ -9275,16 +9384,20 @@
       <c r="F76" s="2">
         <v>3.9079000000000002</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="26">
+      <c r="G76" s="43">
+        <v>2882800</v>
+      </c>
+      <c r="H76" s="43">
+        <v>25080</v>
+      </c>
+      <c r="I76" s="44">
         <v>729400</v>
       </c>
-      <c r="J76" s="26">
+      <c r="J76" s="44">
         <v>6900</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>146</v>
       </c>
@@ -9303,16 +9416,20 @@
       <c r="F77" s="2">
         <v>1.5290999999999999</v>
       </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="26">
+      <c r="G77" s="43">
+        <v>1061500</v>
+      </c>
+      <c r="H77" s="43">
+        <v>9659.5</v>
+      </c>
+      <c r="I77" s="44">
         <v>673100</v>
       </c>
-      <c r="J77" s="26">
+      <c r="J77" s="44">
         <v>9200</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>147</v>
       </c>
@@ -9331,16 +9448,20 @@
       <c r="F78" s="2">
         <v>1.9878</v>
       </c>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="26">
+      <c r="G78" s="43">
+        <v>1472000</v>
+      </c>
+      <c r="H78" s="43">
+        <v>12365</v>
+      </c>
+      <c r="I78" s="44">
         <v>724300</v>
       </c>
-      <c r="J78" s="26">
+      <c r="J78" s="44">
         <v>8100</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>148</v>
       </c>
@@ -9359,16 +9480,20 @@
       <c r="F79" s="2">
         <v>3.6943999999999999</v>
       </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="26">
+      <c r="G79" s="43">
+        <v>2733900</v>
+      </c>
+      <c r="H79" s="43">
+        <v>21325</v>
+      </c>
+      <c r="I79" s="44">
         <v>731300</v>
       </c>
-      <c r="J79" s="26">
+      <c r="J79" s="44">
         <v>6400</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>149</v>
       </c>
@@ -9387,242 +9512,372 @@
       <c r="F80" s="2">
         <v>3.7263999999999999</v>
       </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="26">
+      <c r="G80" s="43">
+        <v>2719700</v>
+      </c>
+      <c r="H80" s="43">
+        <v>22574</v>
+      </c>
+      <c r="I80" s="44">
         <v>724600</v>
       </c>
-      <c r="J80" s="26">
+      <c r="J80" s="44">
         <v>6200</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
+    <row r="81" spans="1:10" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="46">
+        <v>40717</v>
+      </c>
+      <c r="C81" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D81" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="E81" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" s="50">
+        <v>4.9739500000000003</v>
+      </c>
+      <c r="G81" s="51">
+        <v>1830159.7118855852</v>
+      </c>
+      <c r="H81" s="52">
+        <v>22969.250711229975</v>
+      </c>
+      <c r="I81" s="51">
+        <v>360170.65736556082</v>
+      </c>
+      <c r="J81" s="51">
+        <v>4905.8491770276814</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="38">
+        <v>41163</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F82" s="39">
+        <v>5.0449999999999999</v>
+      </c>
+      <c r="G82" s="40">
+        <v>3768957.0271308627</v>
+      </c>
+      <c r="H82" s="41">
+        <v>32142.699590266628</v>
+      </c>
+      <c r="I82" s="40">
+        <v>741167.48579917767</v>
+      </c>
+      <c r="J82" s="40">
+        <v>6913.6679289259037</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="38">
+        <v>41211</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F83" s="39">
+        <v>5.0390100000000002</v>
+      </c>
+      <c r="G83" s="40">
+        <v>3823376.5696027949</v>
+      </c>
+      <c r="H83" s="41">
+        <v>32395.635321665355</v>
+      </c>
+      <c r="I83" s="40">
+        <v>752848.1801641162</v>
+      </c>
+      <c r="J83" s="40">
+        <v>6968.1706584195026</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="38">
+        <v>41239</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F84" s="39">
+        <v>5.0829899999999997</v>
+      </c>
+      <c r="G84" s="40">
+        <v>3931557.3067508894</v>
+      </c>
+      <c r="H84" s="41">
+        <v>10658.879876223842</v>
+      </c>
+      <c r="I84" s="40">
+        <v>754312.28344904014</v>
+      </c>
+      <c r="J84" s="40">
+        <v>7215.724134490004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" s="46">
+        <v>41312</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F85" s="47">
+        <v>4.7955899999999971</v>
+      </c>
+      <c r="G85" s="48">
+        <v>2719401.4309675233</v>
+      </c>
+      <c r="H85" s="49">
+        <v>22636.01943609053</v>
+      </c>
+      <c r="I85" s="48">
+        <v>546753.5627243513</v>
+      </c>
+      <c r="J85" s="48">
+        <v>8708.2892387661268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="B86" s="38">
+        <v>40964</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F86" s="39">
+        <v>5.3481300000000003</v>
+      </c>
+      <c r="G86" s="40">
+        <v>3959547.5002465248</v>
+      </c>
+      <c r="H86" s="41">
+        <v>31805.510365220594</v>
+      </c>
+      <c r="I86" s="40">
+        <v>722149.982731211</v>
+      </c>
+      <c r="J86" s="40">
+        <v>8855.9148912089986</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="B87" s="38">
+        <v>41023</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F87" s="39">
+        <v>3.97899</v>
+      </c>
+      <c r="G87" s="40">
+        <v>2790516.9592133365</v>
+      </c>
+      <c r="H87" s="41">
+        <v>25495.4636472493</v>
+      </c>
+      <c r="I87" s="40">
+        <v>697924.4555872929</v>
+      </c>
+      <c r="J87" s="40">
+        <v>6490.7519201212481</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I81" s="9">
-        <v>748000</v>
-      </c>
-      <c r="J81" s="9">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I82" s="9">
-        <v>706000</v>
-      </c>
-      <c r="J82" s="9">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I83" s="9">
-        <v>666000</v>
-      </c>
-      <c r="J83" s="9">
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I84" s="9">
-        <v>703000</v>
-      </c>
-      <c r="J84" s="9">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I85" s="9">
-        <v>745000</v>
-      </c>
-      <c r="J85" s="9">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I86" s="9">
-        <v>733000</v>
-      </c>
-      <c r="J86" s="9">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I87" s="9">
-        <v>774000</v>
-      </c>
-      <c r="J87" s="9">
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I88" s="9">
-        <v>642000</v>
+        <v>748000</v>
       </c>
       <c r="J88" s="9">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I89" s="9">
-        <v>591000</v>
+        <v>706000</v>
       </c>
       <c r="J89" s="9">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I90" s="9">
-        <v>657000</v>
+        <v>666000</v>
       </c>
       <c r="J90" s="9">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I91" s="9">
-        <v>679000</v>
+        <v>703000</v>
       </c>
       <c r="J91" s="9">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I92" s="9">
-        <v>677000</v>
+        <v>745000</v>
       </c>
       <c r="J92" s="9">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I93" s="9">
-        <v>664000</v>
+        <v>733000</v>
       </c>
       <c r="J93" s="9">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I94" s="9">
-        <v>624000</v>
+        <v>774000</v>
       </c>
       <c r="J94" s="9">
-        <v>7000.0000000000009</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I95" s="9">
-        <v>695000</v>
+        <v>642000</v>
       </c>
       <c r="J95" s="9">
-        <v>7000.0000000000009</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I96" s="9">
-        <v>691000</v>
+        <v>591000</v>
       </c>
       <c r="J96" s="9">
-        <v>7000.0000000000009</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>180</v>
@@ -9631,92 +9886,384 @@
         <v>657000</v>
       </c>
       <c r="J97" s="9">
-        <v>7000.0000000000009</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I98" s="9">
-        <v>716000</v>
+        <v>679000</v>
       </c>
       <c r="J98" s="9">
-        <v>7000.0000000000009</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I99" s="9">
-        <v>693000</v>
+        <v>677000</v>
       </c>
       <c r="J99" s="9">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>180</v>
       </c>
       <c r="I100" s="9">
-        <v>713000</v>
+        <v>664000</v>
       </c>
       <c r="J100" s="9">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="B101" s="33">
+        <v>40920</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="D101" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F101" s="34">
+        <v>5.3073800000000002</v>
+      </c>
+      <c r="G101" s="35">
+        <v>3342748.2960770563</v>
+      </c>
+      <c r="H101" s="36">
+        <v>33575.233734266934</v>
+      </c>
       <c r="I101" s="9">
-        <v>758000</v>
+        <v>624000</v>
       </c>
       <c r="J101" s="9">
         <v>7000.0000000000009</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
+      </c>
+      <c r="B102" s="33">
+        <v>40973</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="D102" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F102" s="34">
+        <v>4.9325999999999999</v>
+      </c>
+      <c r="G102" s="35">
+        <v>3458232.1699979128</v>
+      </c>
+      <c r="H102" s="36">
+        <v>34899.807743715006</v>
+      </c>
       <c r="I102" s="9">
-        <v>692000</v>
+        <v>695000</v>
       </c>
       <c r="J102" s="9">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7000.0000000000009</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
+      </c>
+      <c r="B103" s="33">
+        <v>40997</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="D103" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F103" s="34">
+        <v>5.0372899999999996</v>
+      </c>
+      <c r="G103" s="35">
+        <v>3530097.8280734047</v>
+      </c>
+      <c r="H103" s="36">
+        <v>33387.655345604049</v>
+      </c>
       <c r="I103" s="9">
+        <v>691000</v>
+      </c>
+      <c r="J103" s="9">
+        <v>7000.0000000000009</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B104" s="33">
+        <v>41026</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F104" s="34">
+        <v>4.9633000000000003</v>
+      </c>
+      <c r="G104" s="35">
+        <v>3309483.9355661478</v>
+      </c>
+      <c r="H104" s="36">
+        <v>30762.59704242145</v>
+      </c>
+      <c r="I104" s="9">
+        <v>657000</v>
+      </c>
+      <c r="J104" s="9">
+        <v>7000.0000000000009</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B105" s="33">
+        <v>41039</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F105" s="34">
+        <v>5.0615800000000002</v>
+      </c>
+      <c r="G105" s="35">
+        <v>3656337.1290554381</v>
+      </c>
+      <c r="H105" s="36">
+        <v>33418.564178441738</v>
+      </c>
+      <c r="I105" s="9">
+        <v>716000</v>
+      </c>
+      <c r="J105" s="9">
+        <v>7000.0000000000009</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B106" s="33">
+        <v>41061</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F106" s="34">
+        <v>5.1539999999999999</v>
+      </c>
+      <c r="G106" s="35">
+        <v>3601939.9906726973</v>
+      </c>
+      <c r="H106" s="36">
+        <v>29697.739512257314</v>
+      </c>
+      <c r="I106" s="9">
+        <v>693000</v>
+      </c>
+      <c r="J106" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B107" s="33">
+        <v>41087</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F107" s="34">
+        <v>5.1114100000000002</v>
+      </c>
+      <c r="G107" s="35">
+        <v>3674523.0340607329</v>
+      </c>
+      <c r="H107" s="36">
+        <v>28911.361147147953</v>
+      </c>
+      <c r="I107" s="9">
+        <v>713000</v>
+      </c>
+      <c r="J107" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B108" s="33">
+        <v>41093</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F108" s="34">
+        <v>5.0311500000000002</v>
+      </c>
+      <c r="G108" s="35">
+        <v>3843474.4954350619</v>
+      </c>
+      <c r="H108" s="36">
+        <v>32139.645591815668</v>
+      </c>
+      <c r="I108" s="9">
+        <v>758000</v>
+      </c>
+      <c r="J108" s="9">
+        <v>7000.0000000000009</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B109" s="32"/>
+      <c r="C109" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I109" s="9">
+        <v>692000</v>
+      </c>
+      <c r="J109" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A110" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" s="32"/>
+      <c r="C110" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I110" s="9">
         <v>688000</v>
       </c>
-      <c r="J103" s="9">
+      <c r="J110" s="9">
         <v>5000</v>
       </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A111" s="37"/>
+      <c r="B111" s="38"/>
+      <c r="F111" s="39"/>
+      <c r="G111" s="40"/>
+      <c r="H111" s="41"/>
+      <c r="I111" s="40"/>
+      <c r="J111" s="40"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A112" s="37"/>
+      <c r="B112" s="38"/>
+      <c r="F112" s="39"/>
+      <c r="G112" s="40"/>
+      <c r="H112" s="41"/>
+      <c r="I112" s="40"/>
+      <c r="J112" s="40"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A113" s="37"/>
+      <c r="B113" s="38"/>
+      <c r="F113" s="39"/>
+      <c r="G113" s="40"/>
+      <c r="H113" s="41"/>
+      <c r="I113" s="40"/>
+      <c r="J113" s="40"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="37"/>
+      <c r="B114" s="38"/>
+      <c r="F114" s="39"/>
+      <c r="G114" s="40"/>
+      <c r="H114" s="41"/>
+      <c r="I114" s="40"/>
+      <c r="J114" s="40"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A115" s="37"/>
+      <c r="B115" s="38"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="40"/>
+      <c r="H115" s="41"/>
+      <c r="I115" s="40"/>
+      <c r="J115" s="40"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B116" s="42"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
